--- a/backend/app/scraper/data/cm_upload.xlsx
+++ b/backend/app/scraper/data/cm_upload.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <x:si>
-    <x:t>The Anvaya Beach Resorts Bali - Saturday, September 26, 2026 3:11:59 PM</x:t>
+    <x:t>The Anvaya Beach Resorts Bali - Monday, September 28, 2026 2:34:26 PM</x:t>
   </x:si>
   <x:si>
     <x:t>Deluxe Room</x:t>
@@ -482,7 +482,7 @@
   <x:dimension ref="A1:CZ52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="72.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="71.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="32.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
     <x:col min="4" max="104" width="10.710625" style="0" customWidth="1"/>
@@ -493,307 +493,307 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="2">
-        <x:v>46291</x:v>
+        <x:v>46293</x:v>
       </x:c>
       <x:c r="E1" s="2">
-        <x:v>46292</x:v>
+        <x:v>46294</x:v>
       </x:c>
       <x:c r="F1" s="2">
-        <x:v>46293</x:v>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="G1" s="2">
-        <x:v>46294</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="H1" s="2">
-        <x:v>46295</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="I1" s="2">
-        <x:v>46296</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="J1" s="2">
-        <x:v>46297</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="K1" s="2">
-        <x:v>46298</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="L1" s="2">
-        <x:v>46299</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="M1" s="2">
-        <x:v>46300</x:v>
+        <x:v>46302</x:v>
       </x:c>
       <x:c r="N1" s="2">
-        <x:v>46301</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="O1" s="2">
-        <x:v>46302</x:v>
+        <x:v>46304</x:v>
       </x:c>
       <x:c r="P1" s="2">
-        <x:v>46303</x:v>
+        <x:v>46305</x:v>
       </x:c>
       <x:c r="Q1" s="2">
-        <x:v>46304</x:v>
+        <x:v>46306</x:v>
       </x:c>
       <x:c r="R1" s="2">
-        <x:v>46305</x:v>
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="S1" s="2">
-        <x:v>46306</x:v>
+        <x:v>46308</x:v>
       </x:c>
       <x:c r="T1" s="2">
-        <x:v>46307</x:v>
+        <x:v>46309</x:v>
       </x:c>
       <x:c r="U1" s="2">
-        <x:v>46308</x:v>
+        <x:v>46310</x:v>
       </x:c>
       <x:c r="V1" s="2">
-        <x:v>46309</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="W1" s="2">
-        <x:v>46310</x:v>
+        <x:v>46312</x:v>
       </x:c>
       <x:c r="X1" s="2">
-        <x:v>46311</x:v>
+        <x:v>46313</x:v>
       </x:c>
       <x:c r="Y1" s="2">
-        <x:v>46312</x:v>
+        <x:v>46314</x:v>
       </x:c>
       <x:c r="Z1" s="2">
-        <x:v>46313</x:v>
+        <x:v>46315</x:v>
       </x:c>
       <x:c r="AA1" s="2">
-        <x:v>46314</x:v>
+        <x:v>46316</x:v>
       </x:c>
       <x:c r="AB1" s="2">
-        <x:v>46315</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="AC1" s="2">
-        <x:v>46316</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="AD1" s="2">
-        <x:v>46317</x:v>
+        <x:v>46319</x:v>
       </x:c>
       <x:c r="AE1" s="2">
-        <x:v>46318</x:v>
+        <x:v>46320</x:v>
       </x:c>
       <x:c r="AF1" s="2">
-        <x:v>46319</x:v>
+        <x:v>46321</x:v>
       </x:c>
       <x:c r="AG1" s="2">
-        <x:v>46320</x:v>
+        <x:v>46322</x:v>
       </x:c>
       <x:c r="AH1" s="2">
-        <x:v>46321</x:v>
+        <x:v>46323</x:v>
       </x:c>
       <x:c r="AI1" s="2">
-        <x:v>46322</x:v>
+        <x:v>46324</x:v>
       </x:c>
       <x:c r="AJ1" s="2">
-        <x:v>46323</x:v>
+        <x:v>46325</x:v>
       </x:c>
       <x:c r="AK1" s="2">
-        <x:v>46324</x:v>
+        <x:v>46326</x:v>
       </x:c>
       <x:c r="AL1" s="2">
-        <x:v>46325</x:v>
+        <x:v>46327</x:v>
       </x:c>
       <x:c r="AM1" s="2">
-        <x:v>46326</x:v>
+        <x:v>46328</x:v>
       </x:c>
       <x:c r="AN1" s="2">
-        <x:v>46327</x:v>
+        <x:v>46329</x:v>
       </x:c>
       <x:c r="AO1" s="2">
-        <x:v>46328</x:v>
+        <x:v>46330</x:v>
       </x:c>
       <x:c r="AP1" s="2">
-        <x:v>46329</x:v>
+        <x:v>46331</x:v>
       </x:c>
       <x:c r="AQ1" s="2">
-        <x:v>46330</x:v>
+        <x:v>46332</x:v>
       </x:c>
       <x:c r="AR1" s="2">
-        <x:v>46331</x:v>
+        <x:v>46333</x:v>
       </x:c>
       <x:c r="AS1" s="2">
-        <x:v>46332</x:v>
+        <x:v>46334</x:v>
       </x:c>
       <x:c r="AT1" s="2">
-        <x:v>46333</x:v>
+        <x:v>46335</x:v>
       </x:c>
       <x:c r="AU1" s="2">
-        <x:v>46334</x:v>
+        <x:v>46336</x:v>
       </x:c>
       <x:c r="AV1" s="2">
-        <x:v>46335</x:v>
+        <x:v>46337</x:v>
       </x:c>
       <x:c r="AW1" s="2">
-        <x:v>46336</x:v>
+        <x:v>46338</x:v>
       </x:c>
       <x:c r="AX1" s="2">
-        <x:v>46337</x:v>
+        <x:v>46339</x:v>
       </x:c>
       <x:c r="AY1" s="2">
-        <x:v>46338</x:v>
+        <x:v>46340</x:v>
       </x:c>
       <x:c r="AZ1" s="2">
-        <x:v>46339</x:v>
+        <x:v>46341</x:v>
       </x:c>
       <x:c r="BA1" s="2">
-        <x:v>46340</x:v>
+        <x:v>46342</x:v>
       </x:c>
       <x:c r="BB1" s="2">
-        <x:v>46341</x:v>
+        <x:v>46343</x:v>
       </x:c>
       <x:c r="BC1" s="2">
-        <x:v>46342</x:v>
+        <x:v>46344</x:v>
       </x:c>
       <x:c r="BD1" s="2">
-        <x:v>46343</x:v>
+        <x:v>46345</x:v>
       </x:c>
       <x:c r="BE1" s="2">
-        <x:v>46344</x:v>
+        <x:v>46346</x:v>
       </x:c>
       <x:c r="BF1" s="2">
-        <x:v>46345</x:v>
+        <x:v>46347</x:v>
       </x:c>
       <x:c r="BG1" s="2">
-        <x:v>46346</x:v>
+        <x:v>46348</x:v>
       </x:c>
       <x:c r="BH1" s="2">
-        <x:v>46347</x:v>
+        <x:v>46349</x:v>
       </x:c>
       <x:c r="BI1" s="2">
-        <x:v>46348</x:v>
+        <x:v>46350</x:v>
       </x:c>
       <x:c r="BJ1" s="2">
-        <x:v>46349</x:v>
+        <x:v>46351</x:v>
       </x:c>
       <x:c r="BK1" s="2">
-        <x:v>46350</x:v>
+        <x:v>46352</x:v>
       </x:c>
       <x:c r="BL1" s="2">
-        <x:v>46351</x:v>
+        <x:v>46353</x:v>
       </x:c>
       <x:c r="BM1" s="2">
-        <x:v>46352</x:v>
+        <x:v>46354</x:v>
       </x:c>
       <x:c r="BN1" s="2">
-        <x:v>46353</x:v>
+        <x:v>46355</x:v>
       </x:c>
       <x:c r="BO1" s="2">
-        <x:v>46354</x:v>
+        <x:v>46356</x:v>
       </x:c>
       <x:c r="BP1" s="2">
-        <x:v>46355</x:v>
+        <x:v>46357</x:v>
       </x:c>
       <x:c r="BQ1" s="2">
-        <x:v>46356</x:v>
+        <x:v>46358</x:v>
       </x:c>
       <x:c r="BR1" s="2">
-        <x:v>46357</x:v>
+        <x:v>46359</x:v>
       </x:c>
       <x:c r="BS1" s="2">
-        <x:v>46358</x:v>
+        <x:v>46360</x:v>
       </x:c>
       <x:c r="BT1" s="2">
-        <x:v>46359</x:v>
+        <x:v>46361</x:v>
       </x:c>
       <x:c r="BU1" s="2">
-        <x:v>46360</x:v>
+        <x:v>46362</x:v>
       </x:c>
       <x:c r="BV1" s="2">
-        <x:v>46361</x:v>
+        <x:v>46363</x:v>
       </x:c>
       <x:c r="BW1" s="2">
-        <x:v>46362</x:v>
+        <x:v>46364</x:v>
       </x:c>
       <x:c r="BX1" s="2">
-        <x:v>46363</x:v>
+        <x:v>46365</x:v>
       </x:c>
       <x:c r="BY1" s="2">
-        <x:v>46364</x:v>
+        <x:v>46366</x:v>
       </x:c>
       <x:c r="BZ1" s="2">
-        <x:v>46365</x:v>
+        <x:v>46367</x:v>
       </x:c>
       <x:c r="CA1" s="2">
-        <x:v>46366</x:v>
+        <x:v>46368</x:v>
       </x:c>
       <x:c r="CB1" s="2">
-        <x:v>46367</x:v>
+        <x:v>46369</x:v>
       </x:c>
       <x:c r="CC1" s="2">
-        <x:v>46368</x:v>
+        <x:v>46370</x:v>
       </x:c>
       <x:c r="CD1" s="2">
-        <x:v>46369</x:v>
+        <x:v>46371</x:v>
       </x:c>
       <x:c r="CE1" s="2">
-        <x:v>46370</x:v>
+        <x:v>46372</x:v>
       </x:c>
       <x:c r="CF1" s="2">
-        <x:v>46371</x:v>
+        <x:v>46373</x:v>
       </x:c>
       <x:c r="CG1" s="2">
-        <x:v>46372</x:v>
+        <x:v>46374</x:v>
       </x:c>
       <x:c r="CH1" s="2">
-        <x:v>46373</x:v>
+        <x:v>46375</x:v>
       </x:c>
       <x:c r="CI1" s="2">
-        <x:v>46374</x:v>
+        <x:v>46376</x:v>
       </x:c>
       <x:c r="CJ1" s="2">
-        <x:v>46375</x:v>
+        <x:v>46377</x:v>
       </x:c>
       <x:c r="CK1" s="2">
-        <x:v>46376</x:v>
+        <x:v>46378</x:v>
       </x:c>
       <x:c r="CL1" s="2">
-        <x:v>46377</x:v>
+        <x:v>46379</x:v>
       </x:c>
       <x:c r="CM1" s="2">
-        <x:v>46378</x:v>
+        <x:v>46380</x:v>
       </x:c>
       <x:c r="CN1" s="2">
-        <x:v>46379</x:v>
+        <x:v>46381</x:v>
       </x:c>
       <x:c r="CO1" s="2">
-        <x:v>46380</x:v>
+        <x:v>46382</x:v>
       </x:c>
       <x:c r="CP1" s="2">
-        <x:v>46381</x:v>
+        <x:v>46383</x:v>
       </x:c>
       <x:c r="CQ1" s="2">
-        <x:v>46382</x:v>
+        <x:v>46384</x:v>
       </x:c>
       <x:c r="CR1" s="2">
-        <x:v>46383</x:v>
+        <x:v>46385</x:v>
       </x:c>
       <x:c r="CS1" s="2">
-        <x:v>46384</x:v>
+        <x:v>46386</x:v>
       </x:c>
       <x:c r="CT1" s="2">
-        <x:v>46385</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="CU1" s="2">
-        <x:v>46386</x:v>
+        <x:v>46388</x:v>
       </x:c>
       <x:c r="CV1" s="2">
-        <x:v>46387</x:v>
+        <x:v>46389</x:v>
       </x:c>
       <x:c r="CW1" s="2">
-        <x:v>46388</x:v>
+        <x:v>46390</x:v>
       </x:c>
       <x:c r="CX1" s="2">
-        <x:v>46389</x:v>
+        <x:v>46391</x:v>
       </x:c>
       <x:c r="CY1" s="2">
-        <x:v>46390</x:v>
+        <x:v>46392</x:v>
       </x:c>
       <x:c r="CZ1" s="2">
-        <x:v>46391</x:v>
+        <x:v>46393</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:104">
@@ -804,295 +804,295 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="n">
+      <x:c r="K2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I2" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K2" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L2" s="3" t="n">
+      <x:c r="P2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="n">
+      <x:c r="Q2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="V2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="X2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Y2" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Z2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AA2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="n">
+      <x:c r="AB2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O2" s="3" t="n">
+      <x:c r="AC2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T2" s="3" t="n">
+      <x:c r="AD2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="U2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="V2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="W2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X2" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Y2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Z2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="AA2" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AB2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AC2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AD2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AE2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AF2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AG2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AH2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AI2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AJ2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AK2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AL2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AM2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AN2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AO2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AI2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AJ2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AK2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AL2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AM2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AN2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AO2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="AP2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AQ2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AR2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AS2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AT2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AU2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AV2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AW2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AR2" s="3" t="n">
+      <x:c r="AX2" s="3" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="AS2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AT2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AU2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AV2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AW2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AX2" s="3" t="n">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="AY2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AZ2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BA2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="BB2" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BC2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BE2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BF2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BG2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BH2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BD2" s="3" t="n">
+      <x:c r="BI2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BJ2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BK2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BL2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BE2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BF2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BG2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BH2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BI2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BJ2" s="3" t="n">
+      <x:c r="BM2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BN2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BO2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BP2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BQ2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BK2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BL2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BM2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BN2" s="3" t="n">
+      <x:c r="BR2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BO2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BP2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BQ2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BR2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="BS2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BT2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BU2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BV2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BW2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BX2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BY2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BZ2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CA2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CB2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CC2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CD2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CE2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CF2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CG2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CH2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CI2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CJ2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CK2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CL2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CM2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CN2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CO2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CP2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CQ2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CR2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="CS2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BT2" s="3" t="n">
+      <x:c r="CT2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BU2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BV2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BW2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BX2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BY2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="BZ2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CA2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CB2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CC2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CD2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CE2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CF2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CG2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CH2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CI2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CJ2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CK2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CL2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CM2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CN2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CO2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CP2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CQ2" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="CR2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CS2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="CT2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="CU2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="CV2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="CW2" s="3" t="n">
         <x:v>30</x:v>
@@ -1438,7 +1438,7 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="F4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="G4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1447,10 +1447,10 @@
         <x:v>3168750</x:v>
       </x:c>
       <x:c r="I4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="J4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="K4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1459,28 +1459,28 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="M4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="N4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="O4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="N4" s="5" t="n">
+      <x:c r="P4" s="5" t="n">
         <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="O4" s="5" t="n">
-        <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="P4" s="5" t="n">
-        <x:v>2957500</x:v>
       </x:c>
       <x:c r="Q4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="R4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="S4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="T4" s="5" t="n">
-        <x:v>2535000</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="U4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1489,16 +1489,16 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="W4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="X4" s="5" t="n">
+        <x:v>3168750</x:v>
+      </x:c>
+      <x:c r="Y4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="X4" s="5" t="n">
+      <x:c r="Z4" s="5" t="n">
         <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="Y4" s="5" t="n">
-        <x:v>2429375</x:v>
-      </x:c>
-      <x:c r="Z4" s="5" t="n">
-        <x:v>3168750</x:v>
       </x:c>
       <x:c r="AA4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1510,31 +1510,31 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="AD4" s="5" t="n">
+        <x:v>3168750</x:v>
+      </x:c>
+      <x:c r="AE4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AF4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AG4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="AE4" s="5" t="n">
+      <x:c r="AH4" s="5" t="n">
         <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="AF4" s="5" t="n">
-        <x:v>3168750</x:v>
-      </x:c>
-      <x:c r="AG4" s="5" t="n">
-        <x:v>2429375</x:v>
-      </x:c>
-      <x:c r="AH4" s="5" t="n">
-        <x:v>2429375</x:v>
       </x:c>
       <x:c r="AI4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="AJ4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="AK4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="AL4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="AM4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1543,16 +1543,16 @@
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AO4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="AP4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="AQ4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AP4" s="5" t="n">
+      <x:c r="AR4" s="5" t="n">
         <x:v>2429375</x:v>
-      </x:c>
-      <x:c r="AQ4" s="5" t="n">
-        <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="AR4" s="5" t="n">
-        <x:v>2535000</x:v>
       </x:c>
       <x:c r="AS4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1576,49 +1576,49 @@
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AZ4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="BA4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="BB4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="BC4" s="5" t="n">
+        <x:v>3380000</x:v>
+      </x:c>
+      <x:c r="BD4" s="5" t="n">
         <x:v>2957500</x:v>
       </x:c>
-      <x:c r="BC4" s="5" t="n">
+      <x:c r="BE4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="BF4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="BD4" s="5" t="n">
-        <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="BE4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="BF4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
       <x:c r="BG4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="BH4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="BI4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="BJ4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="BK4" s="5" t="n">
         <x:v>2957500</x:v>
       </x:c>
       <x:c r="BL4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="BM4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="BN4" s="5" t="n">
-        <x:v>2535000</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="BO4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1690,10 +1690,10 @@
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="CL4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="CM4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="CN4" s="5" t="n">
         <x:v>2957500</x:v>
@@ -1702,10 +1702,10 @@
         <x:v>2957500</x:v>
       </x:c>
       <x:c r="CP4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CQ4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CR4" s="5" t="n">
         <x:v>3168750</x:v>
@@ -1714,22 +1714,22 @@
         <x:v>3168750</x:v>
       </x:c>
       <x:c r="CT4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="CU4" s="5" t="n">
         <x:v>3168750</x:v>
       </x:c>
       <x:c r="CV4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CW4" s="5" t="n">
         <x:v>3168750</x:v>
       </x:c>
       <x:c r="CX4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="CY4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="CZ4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1742,59 +1742,59 @@
       <x:c r="C6" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="n">
+      <x:c r="D6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K6" s="3" t="n">
+      <x:c r="J6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="T6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="U6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="U6" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V6" s="3" t="n">
         <x:v>0</x:v>
@@ -1803,58 +1803,58 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="X6" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="Y6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Z6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AA6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AB6" s="3" t="n">
+      <x:c r="AA6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AB6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AC6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AD6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AD6" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE6" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AF6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AI6" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="AH6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AI6" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AJ6" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AK6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AK6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL6" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AN6" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AO6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AP6" s="3" t="n">
         <x:v>2</x:v>
@@ -1869,7 +1869,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AT6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AU6" s="3" t="n">
         <x:v>2</x:v>
@@ -1878,79 +1878,79 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AW6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AX6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AY6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AZ6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BA6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BB6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BC6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BD6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BC6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BD6" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BE6" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="BF6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BG6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="BF6" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="BG6" s="3" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BH6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BI6" s="3" t="n">
+      <x:c r="BI6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BK6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BL6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BM6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BN6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BO6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BP6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BQ6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BR6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BS6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BT6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BJ6" s="3" t="n">
+      <x:c r="BU6" s="3" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="BK6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BL6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BN6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BO6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BP6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BQ6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BR6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BS6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BT6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BU6" s="3" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="BV6" s="3" t="n">
         <x:v>10</x:v>
@@ -1992,58 +1992,58 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="CI6" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="CJ6" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="CK6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CL6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CM6" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CN6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CO6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CP6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="CQ6" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="CR6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CS6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CT6" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="CS6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CT6" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CU6" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="CV6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CW6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="CV6" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CW6" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="CX6" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="CY6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="CZ6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:104">
@@ -2371,25 +2371,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="5" t="n">
+        <x:v>3640000</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="n">
+        <x:v>3412500</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
-      <x:c r="E8" s="5" t="n">
-        <x:v>3640000</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="n">
-        <x:v>3640000</x:v>
-      </x:c>
       <x:c r="G8" s="5" t="n">
-        <x:v>3412500</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="H8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="I8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="J8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="K8" s="5" t="n">
         <x:v>3185000</x:v>
@@ -2398,25 +2398,25 @@
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="M8" s="5" t="n">
+        <x:v>2730000</x:v>
+      </x:c>
+      <x:c r="N8" s="5" t="n">
+        <x:v>2730000</x:v>
+      </x:c>
+      <x:c r="O8" s="5" t="n">
+        <x:v>3412500</x:v>
+      </x:c>
+      <x:c r="P8" s="5" t="n">
+        <x:v>3412500</x:v>
+      </x:c>
+      <x:c r="Q8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
-      <x:c r="N8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="O8" s="5" t="n">
+      <x:c r="R8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="n">
+      <x:c r="S8" s="5" t="n">
         <x:v>2730000</x:v>
-      </x:c>
-      <x:c r="Q8" s="5" t="n">
-        <x:v>3412500</x:v>
-      </x:c>
-      <x:c r="R8" s="5" t="n">
-        <x:v>3412500</x:v>
-      </x:c>
-      <x:c r="S8" s="5" t="n">
-        <x:v>3185000</x:v>
       </x:c>
       <x:c r="T8" s="5" t="n">
         <x:v>2730000</x:v>
@@ -2440,16 +2440,16 @@
         <x:v>2730000</x:v>
       </x:c>
       <x:c r="AA8" s="5" t="n">
+        <x:v>3185000</x:v>
+      </x:c>
+      <x:c r="AB8" s="5" t="n">
+        <x:v>3185000</x:v>
+      </x:c>
+      <x:c r="AC8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
-      <x:c r="AB8" s="5" t="n">
+      <x:c r="AD8" s="5" t="n">
         <x:v>2730000</x:v>
-      </x:c>
-      <x:c r="AC8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="AD8" s="5" t="n">
-        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AE8" s="5" t="n">
         <x:v>2730000</x:v>
@@ -2458,10 +2458,10 @@
         <x:v>2730000</x:v>
       </x:c>
       <x:c r="AG8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AH8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AI8" s="5" t="n">
         <x:v>3185000</x:v>
@@ -2470,13 +2470,13 @@
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="AK8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="AL8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="AM8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="AN8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2515,22 +2515,22 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="AZ8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="BA8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="BB8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="BC8" s="5" t="n">
+        <x:v>2730000</x:v>
+      </x:c>
+      <x:c r="BD8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
-      <x:c r="BD8" s="5" t="n">
-        <x:v>2730000</x:v>
-      </x:c>
       <x:c r="BE8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="BF8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2542,19 +2542,19 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="BI8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="BJ8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="BK8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="BL8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="BM8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="BN8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2641,10 +2641,10 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="CP8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="CQ8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="CR8" s="5" t="n">
         <x:v>3185000</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="CZ8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:104">
@@ -2682,88 +2682,88 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="n">
+      <x:c r="L10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="L10" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="M10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="n">
+      <x:c r="P10" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="n">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="Q10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="R10" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S10" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="T10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="U10" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="V10" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W10" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="X10" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="X10" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y10" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z10" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AA10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AA10" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AB10" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC10" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="AB10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AC10" s="3" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="AD10" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AE10" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AF10" s="3" t="n">
         <x:v>30</x:v>
@@ -2853,13 +2853,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BI10" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BJ10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="BK10" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BL10" s="3" t="n">
         <x:v>30</x:v>
@@ -3316,10 +3316,10 @@
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="F12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="G12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="H12" s="5" t="n">
         <x:v>3367000</x:v>
@@ -3328,88 +3328,88 @@
         <x:v>3367000</x:v>
       </x:c>
       <x:c r="J12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="K12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="L12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="M12" s="5" t="n">
+        <x:v>2765750</x:v>
+      </x:c>
+      <x:c r="N12" s="5" t="n">
+        <x:v>2765750</x:v>
+      </x:c>
+      <x:c r="O12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
-      <x:c r="N12" s="5" t="n">
+      <x:c r="P12" s="5" t="n">
         <x:v>3848000</x:v>
-      </x:c>
-      <x:c r="O12" s="5" t="n">
-        <x:v>2765750</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="n">
-        <x:v>2765750</x:v>
       </x:c>
       <x:c r="Q12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="R12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="S12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="T12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="U12" s="5" t="n">
         <x:v>3367000</x:v>
       </x:c>
       <x:c r="V12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="W12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2886000</x:v>
       </x:c>
       <x:c r="X12" s="5" t="n">
+        <x:v>3848000</x:v>
+      </x:c>
+      <x:c r="Y12" s="5" t="n">
+        <x:v>3848000</x:v>
+      </x:c>
+      <x:c r="Z12" s="5" t="n">
         <x:v>3607500</x:v>
-      </x:c>
-      <x:c r="Y12" s="5" t="n">
-        <x:v>2886000</x:v>
-      </x:c>
-      <x:c r="Z12" s="5" t="n">
-        <x:v>3848000</x:v>
       </x:c>
       <x:c r="AA12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="AB12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="AC12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="AD12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="AE12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AF12" s="5" t="n">
+        <x:v>2765750</x:v>
+      </x:c>
+      <x:c r="AG12" s="5" t="n">
         <x:v>3367000</x:v>
       </x:c>
-      <x:c r="AG12" s="5" t="n">
-        <x:v>2765750</x:v>
-      </x:c>
       <x:c r="AH12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="AI12" s="5" t="n">
         <x:v>3367000</x:v>
       </x:c>
       <x:c r="AJ12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AK12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AL12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3463,13 +3463,13 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BC12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="BD12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BE12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="BF12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3481,16 +3481,16 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BI12" s="5" t="n">
+        <x:v>2886000</x:v>
+      </x:c>
+      <x:c r="BJ12" s="5" t="n">
+        <x:v>3367000</x:v>
+      </x:c>
+      <x:c r="BK12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
-      <x:c r="BJ12" s="5" t="n">
+      <x:c r="BL12" s="5" t="n">
         <x:v>2765750</x:v>
-      </x:c>
-      <x:c r="BK12" s="5" t="n">
-        <x:v>2886000</x:v>
-      </x:c>
-      <x:c r="BL12" s="5" t="n">
-        <x:v>3367000</x:v>
       </x:c>
       <x:c r="BM12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3568,10 +3568,10 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="CL12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="CM12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="CN12" s="5" t="n">
         <x:v>3367000</x:v>
@@ -3580,10 +3580,10 @@
         <x:v>3367000</x:v>
       </x:c>
       <x:c r="CP12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="CQ12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="CR12" s="5" t="n">
         <x:v>3607500</x:v>
@@ -3604,10 +3604,10 @@
         <x:v>3607500</x:v>
       </x:c>
       <x:c r="CX12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="CY12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="CZ12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3626,71 +3626,71 @@
       <x:c r="E14" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="F14" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G14" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L14" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="I14" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P14" s="3" t="n">
-        <x:v>5</x:v>
+      <x:c r="N14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q14" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="R14" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T14" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="U14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="V14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="W14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="U14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="V14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X14" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Y14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Z14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA14" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AA14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB14" s="3" t="n">
         <x:v>2</x:v>
@@ -3699,64 +3699,64 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AD14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AE14" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE14" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AF14" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AG14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AH14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AI14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AJ14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI14" s="3" t="n">
+      <x:c r="AK14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AJ14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AK14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL14" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="AL14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AN14" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="AN14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AO14" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AP14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AQ14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AR14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AR14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AS14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AT14" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AU14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AV14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AW14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AX14" s="3" t="n">
         <x:v>10</x:v>
@@ -3888,34 +3888,34 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="CO14" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CP14" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CQ14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CR14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CS14" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CU14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CV14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CW14" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="CP14" s="3" t="n">
+      <x:c r="CX14" s="3" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="CQ14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CR14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CS14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CT14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CU14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CV14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CW14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CX14" s="3" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="CY14" s="3" t="n">
         <x:v>10</x:v>
@@ -4249,19 +4249,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="5" t="n">
+        <x:v>4784000</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="n">
+        <x:v>4485000</x:v>
+      </x:c>
+      <x:c r="F16" s="5" t="n">
         <x:v>4186000</x:v>
       </x:c>
-      <x:c r="E16" s="5" t="n">
-        <x:v>4784000</x:v>
-      </x:c>
-      <x:c r="F16" s="5" t="n">
-        <x:v>4784000</x:v>
-      </x:c>
       <x:c r="G16" s="5" t="n">
-        <x:v>4485000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="H16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="I16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4282,16 +4282,16 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="O16" s="5" t="n">
+        <x:v>4485000</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="n">
+        <x:v>4485000</x:v>
+      </x:c>
+      <x:c r="Q16" s="5" t="n">
         <x:v>3588000</x:v>
       </x:c>
-      <x:c r="P16" s="5" t="n">
+      <x:c r="R16" s="5" t="n">
         <x:v>3588000</x:v>
-      </x:c>
-      <x:c r="Q16" s="5" t="n">
-        <x:v>4485000</x:v>
-      </x:c>
-      <x:c r="R16" s="5" t="n">
-        <x:v>4485000</x:v>
       </x:c>
       <x:c r="S16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4318,13 +4318,13 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="AA16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="AB16" s="5" t="n">
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="AC16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="AD16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4351,10 +4351,10 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="AL16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="AM16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="AN16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4420,13 +4420,13 @@
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="BI16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="BJ16" s="5" t="n">
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="BK16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="BL16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4519,10 +4519,10 @@
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="CP16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="CQ16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="CR16" s="5" t="n">
         <x:v>4186000</x:v>
@@ -4549,7 +4549,7 @@
         <x:v>4186000</x:v>
       </x:c>
       <x:c r="CZ16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:104">
@@ -4559,56 +4559,56 @@
       <x:c r="C18" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D18" s="3" t="n">
+      <x:c r="D18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I18" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="I18" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="3" t="n">
+      <x:c r="K18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="3" t="n">
+      <x:c r="R18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="M18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S18" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T18" s="3" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="U18" s="3" t="n">
         <x:v>1</x:v>
@@ -4616,248 +4616,248 @@
       <x:c r="V18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W18" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="W18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y18" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="Y18" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AB18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AE18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AF18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AG18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA18" s="3" t="n">
+      <x:c r="AH18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AI18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AJ18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AK18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AN18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AO18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AP18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AQ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AR18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AS18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AT18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AU18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AV18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AX18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AY18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AZ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BA18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BB18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BC18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BE18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BG18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BH18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BI18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BK18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BL18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BM18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BN18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BO18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BP18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BR18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BT18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BX18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BY18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BZ18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CA18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CB18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CC18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CE18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CG18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AB18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AG18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AH18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AI18" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AJ18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AK18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AL18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AM18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AP18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AQ18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AR18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AS18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AT18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AU18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AV18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AW18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AX18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AY18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AZ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BA18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BB18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BC18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BD18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BE18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BF18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BG18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BI18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BJ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BK18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BL18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BN18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BO18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BP18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BQ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BR18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BS18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BT18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BU18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BV18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BZ18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CA18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CB18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CC18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CD18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CE18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CG18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="CH18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="CI18" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="CI18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CJ18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="CK18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CL18" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="CK18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL18" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CM18" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CN18" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CO18" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="CO18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CP18" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CQ18" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="CQ18" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CR18" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CS18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CT18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CU18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CV18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CW18" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CX18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CY18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CZ18" s="3" t="n">
         <x:v>3</x:v>
@@ -5188,19 +5188,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="5" t="n">
+        <x:v>5772000</x:v>
+      </x:c>
+      <x:c r="E20" s="5" t="n">
+        <x:v>5411250</x:v>
+      </x:c>
+      <x:c r="F20" s="5" t="n">
         <x:v>5050500</x:v>
       </x:c>
-      <x:c r="E20" s="5" t="n">
-        <x:v>5772000</x:v>
-      </x:c>
-      <x:c r="F20" s="5" t="n">
-        <x:v>5772000</x:v>
-      </x:c>
       <x:c r="G20" s="5" t="n">
-        <x:v>5411250</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="H20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="I20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5221,16 +5221,16 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="O20" s="5" t="n">
+        <x:v>5411250</x:v>
+      </x:c>
+      <x:c r="P20" s="5" t="n">
+        <x:v>5411250</x:v>
+      </x:c>
+      <x:c r="Q20" s="5" t="n">
         <x:v>4329000</x:v>
       </x:c>
-      <x:c r="P20" s="5" t="n">
+      <x:c r="R20" s="5" t="n">
         <x:v>4329000</x:v>
-      </x:c>
-      <x:c r="Q20" s="5" t="n">
-        <x:v>5411250</x:v>
-      </x:c>
-      <x:c r="R20" s="5" t="n">
-        <x:v>5411250</x:v>
       </x:c>
       <x:c r="S20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5257,13 +5257,13 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="AA20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="AB20" s="5" t="n">
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="AC20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="AD20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5290,10 +5290,10 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="AL20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="AM20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="AN20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5359,13 +5359,13 @@
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="BI20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="BJ20" s="5" t="n">
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="BK20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="BL20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5458,10 +5458,10 @@
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="CP20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="CQ20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="CR20" s="5" t="n">
         <x:v>5050500</x:v>
@@ -5488,7 +5488,7 @@
         <x:v>5050500</x:v>
       </x:c>
       <x:c r="CZ20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:104">
@@ -5498,92 +5498,92 @@
       <x:c r="C22" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D22" s="3" t="n">
+      <x:c r="D22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="H22" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
+      <x:c r="R22" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="S22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="T22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="U22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="V22" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="W22" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X22" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Y22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AA22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Z22" s="3" t="n">
+      <x:c r="AB22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA22" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AC22" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="AC22" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD22" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AE22" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF22" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AG22" s="3" t="n">
         <x:v>3</x:v>
@@ -5592,10 +5592,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AI22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AJ22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AK22" s="3" t="n">
         <x:v>2</x:v>
@@ -5604,10 +5604,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AM22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AN22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AO22" s="3" t="n">
         <x:v>3</x:v>
@@ -5634,7 +5634,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AW22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AX22" s="3" t="n">
         <x:v>3</x:v>
@@ -5643,7 +5643,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AZ22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="BA22" s="3" t="n">
         <x:v>4</x:v>
@@ -5670,91 +5670,91 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="BI22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BK22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BL22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BM22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BN22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BO22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BP22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BR22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BJ22" s="3" t="n">
+      <x:c r="BT22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BU22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BV22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BW22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BX22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BY22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BZ22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CA22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CB22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CC22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CD22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CE22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CF22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CG22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CH22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CI22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CJ22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BK22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BL22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BM22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BN22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BO22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BP22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BQ22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BR22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BS22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BT22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BU22" s="3" t="n">
+      <x:c r="CK22" s="3" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="BV22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BW22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BX22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BY22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BZ22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CA22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CB22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CC22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CD22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CE22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CF22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CG22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CH22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CI22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CJ22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CK22" s="3" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="CL22" s="3" t="n">
         <x:v>4</x:v>
@@ -6298,13 +6298,13 @@
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="BI24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="BJ24" s="5" t="n">
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="BK24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
       <x:c r="BL24" s="5" t="n">
         <x:v>5157750</x:v>
@@ -6397,10 +6397,10 @@
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="CP24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="CQ24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="CR24" s="5" t="n">
         <x:v>6279000</x:v>
@@ -6427,7 +6427,7 @@
         <x:v>6279000</x:v>
       </x:c>
       <x:c r="CZ24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:104">
@@ -6437,20 +6437,20 @@
       <x:c r="C26" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F26" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G26" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H26" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I26" s="3" t="n">
         <x:v>2</x:v>
@@ -6458,50 +6458,50 @@
       <x:c r="J26" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L26" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="K26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q26" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="R26" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="R26" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S26" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="T26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="X26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Y26" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Z26" s="3" t="n">
         <x:v>0</x:v>
@@ -6510,16 +6510,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC26" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC26" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD26" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF26" s="3" t="n">
         <x:v>5</x:v>
@@ -6531,13 +6531,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AI26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AJ26" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AK26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AL26" s="3" t="n">
         <x:v>5</x:v>
@@ -7237,13 +7237,13 @@
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="BI28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="BJ28" s="5" t="n">
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="BK28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
       <x:c r="BL28" s="5" t="n">
         <x:v>5494125</x:v>
@@ -7336,10 +7336,10 @@
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="CP28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="CQ28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="CR28" s="5" t="n">
         <x:v>6688500</x:v>
@@ -7366,7 +7366,7 @@
         <x:v>6688500</x:v>
       </x:c>
       <x:c r="CZ28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:104">
@@ -7385,62 +7385,62 @@
       <x:c r="F30" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H30" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="G30" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J30" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M30" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="O30" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P30" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R30" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q30" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="S30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="T30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U30" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="V30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Y30" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y30" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z30" s="3" t="s">
         <x:v>3</x:v>
@@ -7454,11 +7454,11 @@
       <x:c r="AC30" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AD30" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AD30" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AE30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AF30" s="3" t="n">
         <x:v>3</x:v>
@@ -7479,10 +7479,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AL30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AN30" s="3" t="n">
         <x:v>2</x:v>
@@ -7491,10 +7491,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AP30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AQ30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR30" s="3" t="n">
         <x:v>3</x:v>
@@ -7530,13 +7530,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BC30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BD30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="BE30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BF30" s="3" t="n">
         <x:v>3</x:v>
@@ -8176,13 +8176,13 @@
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="BI32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="BJ32" s="5" t="n">
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="BK32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
       <x:c r="BL32" s="5" t="n">
         <x:v>6877000</x:v>
@@ -8275,10 +8275,10 @@
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="CP32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="CQ32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="CR32" s="5" t="n">
         <x:v>8372000</x:v>
@@ -8305,7 +8305,7 @@
         <x:v>8372000</x:v>
       </x:c>
       <x:c r="CZ32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:104">
@@ -8315,158 +8315,158 @@
       <x:c r="C34" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E34" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="D34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G34" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H34" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J34" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K34" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="L34" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M34" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="O34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q34" s="3" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="V34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R34" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S34" s="3" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="T34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="U34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="V34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Y34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="Z34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AA34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
+      <x:c r="AA34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="AB34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AC34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AC34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="AD34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AE34" s="3" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF34" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AG34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH34" s="3" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AI34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AJ34" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AL34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AO34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AP34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AQ34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AR34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AN34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AO34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AP34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AQ34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AR34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AS34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AT34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AW34" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AX34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AY34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AZ34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BA34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AY34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AZ34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BA34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="BB34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BC34" s="3" t="n">
         <x:v>4</x:v>
@@ -8478,121 +8478,121 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="BF34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BG34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BH34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BJ34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BK34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BL34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BM34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BH34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BI34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BL34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="BN34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BO34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BP34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BQ34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BR34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BP34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BQ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BR34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="BS34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BT34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BU34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BV34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BW34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BX34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BY34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BZ34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CA34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CB34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CC34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CD34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CE34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CF34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CG34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CH34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CI34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CJ34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CK34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CL34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CM34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CN34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CO34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CP34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CQ34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BU34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BV34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BW34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BX34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BY34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BZ34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CA34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CB34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CC34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CD34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CE34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CF34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CG34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CH34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CI34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CJ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CK34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CL34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CM34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CN34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CO34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CP34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CQ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="CR34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="CS34" s="3" t="n">
         <x:v>4</x:v>
@@ -8604,19 +8604,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="CV34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CW34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CX34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CY34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="CW34" s="3" t="n">
+      <x:c r="CZ34" s="3" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="CX34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CY34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CZ34" s="3" t="n">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:104">
@@ -9115,13 +9115,13 @@
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="BI36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="BJ36" s="5" t="n">
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="BK36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
       <x:c r="BL36" s="5" t="n">
         <x:v>7736625</x:v>
@@ -9214,10 +9214,10 @@
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="CP36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="CQ36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="CR36" s="5" t="n">
         <x:v>9418500</x:v>
@@ -9244,7 +9244,7 @@
         <x:v>9418500</x:v>
       </x:c>
       <x:c r="CZ36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:104">
@@ -9254,32 +9254,32 @@
       <x:c r="C38" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F38" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F38" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K38" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M38" s="3" t="n">
         <x:v>2</x:v>
@@ -9288,61 +9288,61 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R38" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="S38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="T38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="U38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="W38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="Z38" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AA38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AC38" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="AC38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AE38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AF38" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AG38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AH38" s="3" t="n">
         <x:v>1</x:v>
@@ -9350,35 +9350,35 @@
       <x:c r="AI38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AJ38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK38" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AJ38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AK38" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AM38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AP38" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AM38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AN38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AO38" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP38" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AQ38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AS38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT38" s="3" t="n">
         <x:v>3</x:v>
@@ -9432,10 +9432,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BK38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BL38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BM38" s="3" t="n">
         <x:v>2</x:v>
@@ -9453,10 +9453,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BR38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BS38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BT38" s="3" t="n">
         <x:v>3</x:v>
@@ -9480,19 +9480,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CA38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CB38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CC38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CD38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CE38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CF38" s="3" t="n">
         <x:v>3</x:v>
@@ -9519,34 +9519,34 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CN38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CO38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CP38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CQ38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CR38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CS38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="CT38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CU38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CV38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CW38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CX38" s="3" t="n">
         <x:v>2</x:v>
@@ -10054,13 +10054,13 @@
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="BI40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="BJ40" s="5" t="n">
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="BK40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
       <x:c r="BL40" s="5" t="n">
         <x:v>7475000</x:v>
@@ -10153,10 +10153,10 @@
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="CP40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="CQ40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="CR40" s="5" t="n">
         <x:v>9100000</x:v>
@@ -10183,7 +10183,7 @@
         <x:v>9100000</x:v>
       </x:c>
       <x:c r="CZ40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:104">
@@ -10196,17 +10196,17 @@
       <x:c r="D42" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E42" s="3" t="n">
+      <x:c r="E42" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G42" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="H42" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I42" s="3" t="n">
         <x:v>0</x:v>
@@ -10215,13 +10215,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M42" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="L42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M42" s="3" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="N42" s="3" t="n">
         <x:v>1</x:v>
@@ -10233,268 +10233,268 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="U42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="V42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="W42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="W42" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="X42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AX42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AY42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AZ42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y42" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Z42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AX42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AY42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AZ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="BA42" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="BB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CE42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CF42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CG42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CE42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CF42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CG42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="CH42" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="CI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CJ42" s="3" t="n">
+      <x:c r="CQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CU42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CV42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CW42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR42" s="3" t="n">
+      <x:c r="CX42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CV42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CW42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CX42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="CY42" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CZ42" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:104">
@@ -11132,29 +11132,29 @@
       <x:c r="C46" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D46" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="D46" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E46" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I46" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="J46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L46" s="3" t="n">
         <x:v>2</x:v>
@@ -11166,13 +11166,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R46" s="3" t="n">
         <x:v>2</x:v>
@@ -11244,10 +11244,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AO46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AP46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AQ46" s="3" t="n">
         <x:v>1</x:v>
@@ -11256,10 +11256,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AU46" s="3" t="n">
         <x:v>2</x:v>
@@ -11286,10 +11286,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BC46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BE46" s="3" t="n">
         <x:v>1</x:v>
@@ -11298,10 +11298,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BG46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BH46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BI46" s="3" t="n">
         <x:v>2</x:v>
@@ -11932,13 +11932,13 @@
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="BI48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="BJ48" s="5" t="n">
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="BK48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
       <x:c r="BL48" s="5" t="n">
         <x:v>9941750</x:v>
@@ -12031,10 +12031,10 @@
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="CP48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="CQ48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="CR48" s="5" t="n">
         <x:v>12103000</x:v>
@@ -12061,7 +12061,7 @@
         <x:v>12103000</x:v>
       </x:c>
       <x:c r="CZ48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:104">
@@ -12074,8 +12074,8 @@
       <x:c r="D50" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="E50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F50" s="3" t="n">
         <x:v>1</x:v>
@@ -12120,10 +12120,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T50" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="U50" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V50" s="3" t="n">
         <x:v>1</x:v>
@@ -12149,11 +12149,11 @@
       <x:c r="AC50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AD50" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="AD50" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AE50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF50" s="3" t="s">
         <x:v>3</x:v>
@@ -12173,11 +12173,11 @@
       <x:c r="AK50" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AL50" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AM50" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AL50" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM50" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AN50" s="3" t="n">
         <x:v>1</x:v>
@@ -12212,14 +12212,14 @@
       <x:c r="AX50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="AY50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AZ50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BA50" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="BA50" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB50" s="3" t="n">
         <x:v>1</x:v>

--- a/backend/app/scraper/data/cm_upload.xlsx
+++ b/backend/app/scraper/data/cm_upload.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <x:si>
-    <x:t>The Anvaya Beach Resorts Bali - Monday, September 28, 2026 2:34:26 PM</x:t>
+    <x:t>The Anvaya Beach Resorts Bali - Thursday, October 1, 2026 7:00:19 AM</x:t>
   </x:si>
   <x:si>
     <x:t>Deluxe Room</x:t>
@@ -482,7 +482,7 @@
   <x:dimension ref="A1:CZ52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="71.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="68.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="32.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.710625" style="0" customWidth="1"/>
     <x:col min="4" max="104" width="10.710625" style="0" customWidth="1"/>
@@ -493,307 +493,307 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D1" s="2">
-        <x:v>46293</x:v>
+        <x:v>46296</x:v>
       </x:c>
       <x:c r="E1" s="2">
-        <x:v>46294</x:v>
+        <x:v>46297</x:v>
       </x:c>
       <x:c r="F1" s="2">
-        <x:v>46295</x:v>
+        <x:v>46298</x:v>
       </x:c>
       <x:c r="G1" s="2">
-        <x:v>46296</x:v>
+        <x:v>46299</x:v>
       </x:c>
       <x:c r="H1" s="2">
-        <x:v>46297</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="I1" s="2">
-        <x:v>46298</x:v>
+        <x:v>46301</x:v>
       </x:c>
       <x:c r="J1" s="2">
-        <x:v>46299</x:v>
+        <x:v>46302</x:v>
       </x:c>
       <x:c r="K1" s="2">
-        <x:v>46300</x:v>
+        <x:v>46303</x:v>
       </x:c>
       <x:c r="L1" s="2">
-        <x:v>46301</x:v>
+        <x:v>46304</x:v>
       </x:c>
       <x:c r="M1" s="2">
-        <x:v>46302</x:v>
+        <x:v>46305</x:v>
       </x:c>
       <x:c r="N1" s="2">
-        <x:v>46303</x:v>
+        <x:v>46306</x:v>
       </x:c>
       <x:c r="O1" s="2">
-        <x:v>46304</x:v>
+        <x:v>46307</x:v>
       </x:c>
       <x:c r="P1" s="2">
-        <x:v>46305</x:v>
+        <x:v>46308</x:v>
       </x:c>
       <x:c r="Q1" s="2">
-        <x:v>46306</x:v>
+        <x:v>46309</x:v>
       </x:c>
       <x:c r="R1" s="2">
-        <x:v>46307</x:v>
+        <x:v>46310</x:v>
       </x:c>
       <x:c r="S1" s="2">
-        <x:v>46308</x:v>
+        <x:v>46311</x:v>
       </x:c>
       <x:c r="T1" s="2">
-        <x:v>46309</x:v>
+        <x:v>46312</x:v>
       </x:c>
       <x:c r="U1" s="2">
-        <x:v>46310</x:v>
+        <x:v>46313</x:v>
       </x:c>
       <x:c r="V1" s="2">
-        <x:v>46311</x:v>
+        <x:v>46314</x:v>
       </x:c>
       <x:c r="W1" s="2">
-        <x:v>46312</x:v>
+        <x:v>46315</x:v>
       </x:c>
       <x:c r="X1" s="2">
-        <x:v>46313</x:v>
+        <x:v>46316</x:v>
       </x:c>
       <x:c r="Y1" s="2">
-        <x:v>46314</x:v>
+        <x:v>46317</x:v>
       </x:c>
       <x:c r="Z1" s="2">
-        <x:v>46315</x:v>
+        <x:v>46318</x:v>
       </x:c>
       <x:c r="AA1" s="2">
-        <x:v>46316</x:v>
+        <x:v>46319</x:v>
       </x:c>
       <x:c r="AB1" s="2">
-        <x:v>46317</x:v>
+        <x:v>46320</x:v>
       </x:c>
       <x:c r="AC1" s="2">
-        <x:v>46318</x:v>
+        <x:v>46321</x:v>
       </x:c>
       <x:c r="AD1" s="2">
-        <x:v>46319</x:v>
+        <x:v>46322</x:v>
       </x:c>
       <x:c r="AE1" s="2">
-        <x:v>46320</x:v>
+        <x:v>46323</x:v>
       </x:c>
       <x:c r="AF1" s="2">
-        <x:v>46321</x:v>
+        <x:v>46324</x:v>
       </x:c>
       <x:c r="AG1" s="2">
-        <x:v>46322</x:v>
+        <x:v>46325</x:v>
       </x:c>
       <x:c r="AH1" s="2">
-        <x:v>46323</x:v>
+        <x:v>46326</x:v>
       </x:c>
       <x:c r="AI1" s="2">
-        <x:v>46324</x:v>
+        <x:v>46327</x:v>
       </x:c>
       <x:c r="AJ1" s="2">
-        <x:v>46325</x:v>
+        <x:v>46328</x:v>
       </x:c>
       <x:c r="AK1" s="2">
-        <x:v>46326</x:v>
+        <x:v>46329</x:v>
       </x:c>
       <x:c r="AL1" s="2">
-        <x:v>46327</x:v>
+        <x:v>46330</x:v>
       </x:c>
       <x:c r="AM1" s="2">
-        <x:v>46328</x:v>
+        <x:v>46331</x:v>
       </x:c>
       <x:c r="AN1" s="2">
-        <x:v>46329</x:v>
+        <x:v>46332</x:v>
       </x:c>
       <x:c r="AO1" s="2">
-        <x:v>46330</x:v>
+        <x:v>46333</x:v>
       </x:c>
       <x:c r="AP1" s="2">
-        <x:v>46331</x:v>
+        <x:v>46334</x:v>
       </x:c>
       <x:c r="AQ1" s="2">
-        <x:v>46332</x:v>
+        <x:v>46335</x:v>
       </x:c>
       <x:c r="AR1" s="2">
-        <x:v>46333</x:v>
+        <x:v>46336</x:v>
       </x:c>
       <x:c r="AS1" s="2">
-        <x:v>46334</x:v>
+        <x:v>46337</x:v>
       </x:c>
       <x:c r="AT1" s="2">
-        <x:v>46335</x:v>
+        <x:v>46338</x:v>
       </x:c>
       <x:c r="AU1" s="2">
-        <x:v>46336</x:v>
+        <x:v>46339</x:v>
       </x:c>
       <x:c r="AV1" s="2">
-        <x:v>46337</x:v>
+        <x:v>46340</x:v>
       </x:c>
       <x:c r="AW1" s="2">
-        <x:v>46338</x:v>
+        <x:v>46341</x:v>
       </x:c>
       <x:c r="AX1" s="2">
-        <x:v>46339</x:v>
+        <x:v>46342</x:v>
       </x:c>
       <x:c r="AY1" s="2">
-        <x:v>46340</x:v>
+        <x:v>46343</x:v>
       </x:c>
       <x:c r="AZ1" s="2">
-        <x:v>46341</x:v>
+        <x:v>46344</x:v>
       </x:c>
       <x:c r="BA1" s="2">
-        <x:v>46342</x:v>
+        <x:v>46345</x:v>
       </x:c>
       <x:c r="BB1" s="2">
-        <x:v>46343</x:v>
+        <x:v>46346</x:v>
       </x:c>
       <x:c r="BC1" s="2">
-        <x:v>46344</x:v>
+        <x:v>46347</x:v>
       </x:c>
       <x:c r="BD1" s="2">
-        <x:v>46345</x:v>
+        <x:v>46348</x:v>
       </x:c>
       <x:c r="BE1" s="2">
-        <x:v>46346</x:v>
+        <x:v>46349</x:v>
       </x:c>
       <x:c r="BF1" s="2">
-        <x:v>46347</x:v>
+        <x:v>46350</x:v>
       </x:c>
       <x:c r="BG1" s="2">
-        <x:v>46348</x:v>
+        <x:v>46351</x:v>
       </x:c>
       <x:c r="BH1" s="2">
-        <x:v>46349</x:v>
+        <x:v>46352</x:v>
       </x:c>
       <x:c r="BI1" s="2">
-        <x:v>46350</x:v>
+        <x:v>46353</x:v>
       </x:c>
       <x:c r="BJ1" s="2">
-        <x:v>46351</x:v>
+        <x:v>46354</x:v>
       </x:c>
       <x:c r="BK1" s="2">
-        <x:v>46352</x:v>
+        <x:v>46355</x:v>
       </x:c>
       <x:c r="BL1" s="2">
-        <x:v>46353</x:v>
+        <x:v>46356</x:v>
       </x:c>
       <x:c r="BM1" s="2">
-        <x:v>46354</x:v>
+        <x:v>46357</x:v>
       </x:c>
       <x:c r="BN1" s="2">
-        <x:v>46355</x:v>
+        <x:v>46358</x:v>
       </x:c>
       <x:c r="BO1" s="2">
-        <x:v>46356</x:v>
+        <x:v>46359</x:v>
       </x:c>
       <x:c r="BP1" s="2">
-        <x:v>46357</x:v>
+        <x:v>46360</x:v>
       </x:c>
       <x:c r="BQ1" s="2">
-        <x:v>46358</x:v>
+        <x:v>46361</x:v>
       </x:c>
       <x:c r="BR1" s="2">
-        <x:v>46359</x:v>
+        <x:v>46362</x:v>
       </x:c>
       <x:c r="BS1" s="2">
-        <x:v>46360</x:v>
+        <x:v>46363</x:v>
       </x:c>
       <x:c r="BT1" s="2">
-        <x:v>46361</x:v>
+        <x:v>46364</x:v>
       </x:c>
       <x:c r="BU1" s="2">
-        <x:v>46362</x:v>
+        <x:v>46365</x:v>
       </x:c>
       <x:c r="BV1" s="2">
-        <x:v>46363</x:v>
+        <x:v>46366</x:v>
       </x:c>
       <x:c r="BW1" s="2">
-        <x:v>46364</x:v>
+        <x:v>46367</x:v>
       </x:c>
       <x:c r="BX1" s="2">
-        <x:v>46365</x:v>
+        <x:v>46368</x:v>
       </x:c>
       <x:c r="BY1" s="2">
-        <x:v>46366</x:v>
+        <x:v>46369</x:v>
       </x:c>
       <x:c r="BZ1" s="2">
-        <x:v>46367</x:v>
+        <x:v>46370</x:v>
       </x:c>
       <x:c r="CA1" s="2">
-        <x:v>46368</x:v>
+        <x:v>46371</x:v>
       </x:c>
       <x:c r="CB1" s="2">
-        <x:v>46369</x:v>
+        <x:v>46372</x:v>
       </x:c>
       <x:c r="CC1" s="2">
-        <x:v>46370</x:v>
+        <x:v>46373</x:v>
       </x:c>
       <x:c r="CD1" s="2">
-        <x:v>46371</x:v>
+        <x:v>46374</x:v>
       </x:c>
       <x:c r="CE1" s="2">
-        <x:v>46372</x:v>
+        <x:v>46375</x:v>
       </x:c>
       <x:c r="CF1" s="2">
-        <x:v>46373</x:v>
+        <x:v>46376</x:v>
       </x:c>
       <x:c r="CG1" s="2">
-        <x:v>46374</x:v>
+        <x:v>46377</x:v>
       </x:c>
       <x:c r="CH1" s="2">
-        <x:v>46375</x:v>
+        <x:v>46378</x:v>
       </x:c>
       <x:c r="CI1" s="2">
-        <x:v>46376</x:v>
+        <x:v>46379</x:v>
       </x:c>
       <x:c r="CJ1" s="2">
-        <x:v>46377</x:v>
+        <x:v>46380</x:v>
       </x:c>
       <x:c r="CK1" s="2">
-        <x:v>46378</x:v>
+        <x:v>46381</x:v>
       </x:c>
       <x:c r="CL1" s="2">
-        <x:v>46379</x:v>
+        <x:v>46382</x:v>
       </x:c>
       <x:c r="CM1" s="2">
-        <x:v>46380</x:v>
+        <x:v>46383</x:v>
       </x:c>
       <x:c r="CN1" s="2">
-        <x:v>46381</x:v>
+        <x:v>46384</x:v>
       </x:c>
       <x:c r="CO1" s="2">
-        <x:v>46382</x:v>
+        <x:v>46385</x:v>
       </x:c>
       <x:c r="CP1" s="2">
-        <x:v>46383</x:v>
+        <x:v>46386</x:v>
       </x:c>
       <x:c r="CQ1" s="2">
-        <x:v>46384</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="CR1" s="2">
-        <x:v>46385</x:v>
+        <x:v>46388</x:v>
       </x:c>
       <x:c r="CS1" s="2">
-        <x:v>46386</x:v>
+        <x:v>46389</x:v>
       </x:c>
       <x:c r="CT1" s="2">
-        <x:v>46387</x:v>
+        <x:v>46390</x:v>
       </x:c>
       <x:c r="CU1" s="2">
-        <x:v>46388</x:v>
+        <x:v>46391</x:v>
       </x:c>
       <x:c r="CV1" s="2">
-        <x:v>46389</x:v>
+        <x:v>46392</x:v>
       </x:c>
       <x:c r="CW1" s="2">
-        <x:v>46390</x:v>
+        <x:v>46393</x:v>
       </x:c>
       <x:c r="CX1" s="2">
-        <x:v>46391</x:v>
+        <x:v>46394</x:v>
       </x:c>
       <x:c r="CY1" s="2">
-        <x:v>46392</x:v>
+        <x:v>46395</x:v>
       </x:c>
       <x:c r="CZ1" s="2">
-        <x:v>46393</x:v>
+        <x:v>46396</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:104">
@@ -803,143 +803,143 @@
       <x:c r="C2" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="n">
+      <x:c r="D2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="n">
+      <x:c r="G2" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="I2" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J2" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="n">
+      <x:c r="M2" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="P2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M2" s="3" t="n">
+      <x:c r="U2" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="V2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X2" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y2" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q2" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="V2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="W2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="X2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="Y2" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Z2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AA2" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="AB2" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AC2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AD2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AE2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AF2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AF2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="AG2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AH2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="AI2" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AJ2" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AK2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AL2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AM2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AN2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AO2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AP2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="AQ2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AP2" s="3" t="n">
+      <x:c r="AR2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="AQ2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="AR2" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="AS2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AT2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AU2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AV2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AW2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AX2" s="3" t="n">
         <x:v>10</x:v>
@@ -951,58 +951,58 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BA2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BB2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BC2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BD2" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="BE2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BB2" s="3" t="n">
+      <x:c r="BF2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BG2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BH2" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BI2" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BC2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BD2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BE2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BF2" s="3" t="n">
+      <x:c r="BJ2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BG2" s="3" t="n">
+      <x:c r="BK2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="BH2" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="BI2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BK2" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="BL2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BM2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="BN2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BO2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BP2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="BQ2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BR2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BS2" s="3" t="n">
         <x:v>30</x:v>
@@ -1074,19 +1074,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="CP2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="CQ2" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="CR2" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="CS2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="CT2" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="CU2" s="3" t="n">
         <x:v>30</x:v>
@@ -1438,34 +1438,34 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="F4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="G4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="H4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="I4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="J4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="K4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="L4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="M4" s="5" t="n">
+        <x:v>3380000</x:v>
+      </x:c>
+      <x:c r="N4" s="5" t="n">
+        <x:v>3380000</x:v>
+      </x:c>
+      <x:c r="O4" s="5" t="n">
         <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="N4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
-      <x:c r="O4" s="5" t="n">
-        <x:v>3380000</x:v>
       </x:c>
       <x:c r="P4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1474,13 +1474,13 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="R4" s="5" t="n">
-        <x:v>2535000</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="S4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="T4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="U4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1489,10 +1489,10 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="W4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="X4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="Y4" s="5" t="n">
         <x:v>3380000</x:v>
@@ -1501,64 +1501,64 @@
         <x:v>3380000</x:v>
       </x:c>
       <x:c r="AA4" s="5" t="n">
+        <x:v>3168750</x:v>
+      </x:c>
+      <x:c r="AB4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AC4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AD4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="AB4" s="5" t="n">
+      <x:c r="AE4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="AC4" s="5" t="n">
+      <x:c r="AF4" s="5" t="n">
         <x:v>3380000</x:v>
       </x:c>
-      <x:c r="AD4" s="5" t="n">
-        <x:v>3168750</x:v>
-      </x:c>
-      <x:c r="AE4" s="5" t="n">
+      <x:c r="AG4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="AH4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AF4" s="5" t="n">
+      <x:c r="AI4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AG4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="AH4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="AI4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
       <x:c r="AJ4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="AK4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AL4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="AM4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="AN4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AO4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AP4" s="5" t="n">
+        <x:v>2429375</x:v>
+      </x:c>
+      <x:c r="AQ4" s="5" t="n">
         <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="AP4" s="5" t="n">
-        <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="AQ4" s="5" t="n">
-        <x:v>2429375</x:v>
       </x:c>
       <x:c r="AR4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AS4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2535000</x:v>
       </x:c>
       <x:c r="AT4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="AU4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1567,52 +1567,52 @@
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="AW4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="AX4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="AY4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="AZ4" s="5" t="n">
+        <x:v>3380000</x:v>
+      </x:c>
+      <x:c r="BA4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="BB4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="BC4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AX4" s="5" t="n">
+      <x:c r="BD4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AY4" s="5" t="n">
+      <x:c r="BE4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="AZ4" s="5" t="n">
+      <x:c r="BF4" s="5" t="n">
         <x:v>2957500</x:v>
       </x:c>
-      <x:c r="BA4" s="5" t="n">
+      <x:c r="BG4" s="5" t="n">
+        <x:v>3380000</x:v>
+      </x:c>
+      <x:c r="BH4" s="5" t="n">
+        <x:v>2957500</x:v>
+      </x:c>
+      <x:c r="BI4" s="5" t="n">
+        <x:v>2535000</x:v>
+      </x:c>
+      <x:c r="BJ4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="BB4" s="5" t="n">
-        <x:v>2535000</x:v>
-      </x:c>
-      <x:c r="BC4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="BD4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
-      <x:c r="BE4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
-      <x:c r="BF4" s="5" t="n">
+      <x:c r="BK4" s="5" t="n">
         <x:v>2429375</x:v>
       </x:c>
-      <x:c r="BG4" s="5" t="n">
+      <x:c r="BL4" s="5" t="n">
         <x:v>2429375</x:v>
-      </x:c>
-      <x:c r="BH4" s="5" t="n">
-        <x:v>2429375</x:v>
-      </x:c>
-      <x:c r="BI4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
-      <x:c r="BJ4" s="5" t="n">
-        <x:v>3380000</x:v>
-      </x:c>
-      <x:c r="BK4" s="5" t="n">
-        <x:v>2957500</x:v>
-      </x:c>
-      <x:c r="BL4" s="5" t="n">
-        <x:v>2535000</x:v>
       </x:c>
       <x:c r="BM4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1681,31 +1681,31 @@
         <x:v>2429375</x:v>
       </x:c>
       <x:c r="CI4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="CJ4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="CK4" s="5" t="n">
-        <x:v>2429375</x:v>
+        <x:v>2957500</x:v>
       </x:c>
       <x:c r="CL4" s="5" t="n">
         <x:v>2957500</x:v>
       </x:c>
       <x:c r="CM4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CN4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CO4" s="5" t="n">
-        <x:v>2957500</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CP4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="CQ4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>3380000</x:v>
       </x:c>
       <x:c r="CR4" s="5" t="n">
         <x:v>3168750</x:v>
@@ -1714,16 +1714,16 @@
         <x:v>3168750</x:v>
       </x:c>
       <x:c r="CT4" s="5" t="n">
-        <x:v>3380000</x:v>
+        <x:v>3168750</x:v>
       </x:c>
       <x:c r="CU4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="CV4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="CW4" s="5" t="n">
-        <x:v>3168750</x:v>
+        <x:v>2429375</x:v>
       </x:c>
       <x:c r="CX4" s="5" t="n">
         <x:v>2429375</x:v>
@@ -1742,59 +1742,59 @@
       <x:c r="C6" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="n">
+      <x:c r="G6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="R6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="U6" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V6" s="3" t="n">
         <x:v>0</x:v>
@@ -1802,44 +1802,44 @@
       <x:c r="W6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Y6" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="X6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y6" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AA6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AA6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB6" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AC6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AD6" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AD6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AG6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AI6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AJ6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AE6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AF6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AG6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AH6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AI6" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ6" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AK6" s="3" t="n">
         <x:v>2</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AM6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AN6" s="3" t="n">
         <x:v>2</x:v>
@@ -1860,67 +1860,67 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AQ6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AR6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AS6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AT6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AU6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AW6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AW6" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AY6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AZ6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BA6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BB6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BC6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BD6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BE6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BF6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AZ6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BA6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BB6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BC6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BG6" s="3" t="n">
+      <x:c r="BD6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BH6" s="3" t="n">
+      <x:c r="BE6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="BI6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BJ6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BK6" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="BF6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BG6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BH6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BI6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BJ6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BK6" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BL6" s="3" t="n">
         <x:v>2</x:v>
@@ -1929,22 +1929,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="BN6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BO6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BP6" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="BQ6" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BR6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BS6" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="BT6" s="3" t="n">
         <x:v>10</x:v>
@@ -1983,67 +1983,67 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="CF6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CG6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CH6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CI6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CJ6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CK6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CL6" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CN6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="CO6" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="CP6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CQ6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CR6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CS6" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CU6" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CV6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="CG6" s="3" t="n">
+      <x:c r="CW6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="CH6" s="3" t="n">
+      <x:c r="CX6" s="3" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="CI6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CJ6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CK6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CL6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CM6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CN6" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CO6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CQ6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CR6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CS6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CT6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CU6" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CV6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CW6" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CX6" s="3" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="CY6" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="CZ6" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:104">
@@ -2371,10 +2371,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="5" t="n">
-        <x:v>3640000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="E8" s="5" t="n">
-        <x:v>3412500</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="F8" s="5" t="n">
         <x:v>3185000</x:v>
@@ -2383,34 +2383,34 @@
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="H8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="I8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="J8" s="5" t="n">
+        <x:v>2730000</x:v>
+      </x:c>
+      <x:c r="K8" s="5" t="n">
+        <x:v>2730000</x:v>
+      </x:c>
+      <x:c r="L8" s="5" t="n">
+        <x:v>3412500</x:v>
+      </x:c>
+      <x:c r="M8" s="5" t="n">
+        <x:v>3412500</x:v>
+      </x:c>
+      <x:c r="N8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
-      <x:c r="K8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="L8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="M8" s="5" t="n">
+      <x:c r="O8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
-      <x:c r="N8" s="5" t="n">
+      <x:c r="P8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
-      <x:c r="O8" s="5" t="n">
-        <x:v>3412500</x:v>
-      </x:c>
-      <x:c r="P8" s="5" t="n">
-        <x:v>3412500</x:v>
-      </x:c>
       <x:c r="Q8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="R8" s="5" t="n">
         <x:v>2730000</x:v>
@@ -2431,46 +2431,46 @@
         <x:v>2730000</x:v>
       </x:c>
       <x:c r="X8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="Y8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="Z8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
       <x:c r="AA8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="AB8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="AC8" s="5" t="n">
         <x:v>2730000</x:v>
       </x:c>
       <x:c r="AD8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AE8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AF8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AG8" s="5" t="n">
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="AH8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="AI8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="AJ8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="AK8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="AL8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2506,25 +2506,25 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="AW8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="AX8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="AY8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="AZ8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2730000</x:v>
       </x:c>
       <x:c r="BA8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="BB8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="BC8" s="5" t="n">
-        <x:v>2730000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="BD8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2533,22 +2533,22 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="BF8" s="5" t="n">
+        <x:v>3185000</x:v>
+      </x:c>
+      <x:c r="BG8" s="5" t="n">
+        <x:v>3185000</x:v>
+      </x:c>
+      <x:c r="BH8" s="5" t="n">
+        <x:v>3185000</x:v>
+      </x:c>
+      <x:c r="BI8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
-      <x:c r="BG8" s="5" t="n">
+      <x:c r="BJ8" s="5" t="n">
         <x:v>2616250</x:v>
       </x:c>
-      <x:c r="BH8" s="5" t="n">
+      <x:c r="BK8" s="5" t="n">
         <x:v>2616250</x:v>
-      </x:c>
-      <x:c r="BI8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="BJ8" s="5" t="n">
-        <x:v>3185000</x:v>
-      </x:c>
-      <x:c r="BK8" s="5" t="n">
-        <x:v>3185000</x:v>
       </x:c>
       <x:c r="BL8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2632,13 +2632,13 @@
         <x:v>2616250</x:v>
       </x:c>
       <x:c r="CM8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="CN8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="CO8" s="5" t="n">
-        <x:v>2616250</x:v>
+        <x:v>3185000</x:v>
       </x:c>
       <x:c r="CP8" s="5" t="n">
         <x:v>3185000</x:v>
@@ -2662,13 +2662,13 @@
         <x:v>3185000</x:v>
       </x:c>
       <x:c r="CW8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="CX8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="CY8" s="5" t="n">
-        <x:v>3185000</x:v>
+        <x:v>2616250</x:v>
       </x:c>
       <x:c r="CZ8" s="5" t="n">
         <x:v>2616250</x:v>
@@ -2682,91 +2682,91 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G10" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="n">
+      <x:c r="I10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="n">
+      <x:c r="J10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="n">
+      <x:c r="K10" s="3" t="n">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="n">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="n">
+      <x:c r="P10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O10" s="3" t="n">
+      <x:c r="Q10" s="3" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S10" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="T10" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="U10" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="V10" s="3" t="n">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="S10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="T10" s="3" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="U10" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="V10" s="3" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="W10" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="X10" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Y10" s="3" t="n">
+      <x:c r="X10" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y10" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z10" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Z10" s="3" t="n">
+      <x:c r="AA10" s="3" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="AB10" s="3" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="AA10" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB10" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AC10" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="AD10" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="AE10" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AF10" s="3" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AG10" s="3" t="n">
         <x:v>30</x:v>
@@ -2853,7 +2853,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="BI10" s="3" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BJ10" s="3" t="n">
         <x:v>30</x:v>
@@ -3316,58 +3316,58 @@
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="F12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="G12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="H12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="I12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3848000</x:v>
       </x:c>
       <x:c r="J12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="K12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="L12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="M12" s="5" t="n">
+        <x:v>3848000</x:v>
+      </x:c>
+      <x:c r="N12" s="5" t="n">
+        <x:v>3848000</x:v>
+      </x:c>
+      <x:c r="O12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
-      <x:c r="N12" s="5" t="n">
-        <x:v>2765750</x:v>
-      </x:c>
-      <x:c r="O12" s="5" t="n">
+      <x:c r="P12" s="5" t="n">
+        <x:v>3367000</x:v>
+      </x:c>
+      <x:c r="Q12" s="5" t="n">
+        <x:v>3367000</x:v>
+      </x:c>
+      <x:c r="R12" s="5" t="n">
+        <x:v>3607500</x:v>
+      </x:c>
+      <x:c r="S12" s="5" t="n">
+        <x:v>3607500</x:v>
+      </x:c>
+      <x:c r="T12" s="5" t="n">
+        <x:v>2886000</x:v>
+      </x:c>
+      <x:c r="U12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
-      <x:c r="P12" s="5" t="n">
+      <x:c r="V12" s="5" t="n">
         <x:v>3848000</x:v>
       </x:c>
-      <x:c r="Q12" s="5" t="n">
-        <x:v>3848000</x:v>
-      </x:c>
-      <x:c r="R12" s="5" t="n">
-        <x:v>2765750</x:v>
-      </x:c>
-      <x:c r="S12" s="5" t="n">
-        <x:v>3367000</x:v>
-      </x:c>
-      <x:c r="T12" s="5" t="n">
-        <x:v>3367000</x:v>
-      </x:c>
-      <x:c r="U12" s="5" t="n">
-        <x:v>3367000</x:v>
-      </x:c>
-      <x:c r="V12" s="5" t="n">
+      <x:c r="W12" s="5" t="n">
         <x:v>3607500</x:v>
-      </x:c>
-      <x:c r="W12" s="5" t="n">
-        <x:v>2886000</x:v>
       </x:c>
       <x:c r="X12" s="5" t="n">
         <x:v>3848000</x:v>
@@ -3376,34 +3376,34 @@
         <x:v>3848000</x:v>
       </x:c>
       <x:c r="Z12" s="5" t="n">
+        <x:v>3848000</x:v>
+      </x:c>
+      <x:c r="AA12" s="5" t="n">
         <x:v>3607500</x:v>
       </x:c>
-      <x:c r="AA12" s="5" t="n">
-        <x:v>3848000</x:v>
-      </x:c>
       <x:c r="AB12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AC12" s="5" t="n">
-        <x:v>3848000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AD12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="AE12" s="5" t="n">
+        <x:v>3367000</x:v>
+      </x:c>
+      <x:c r="AF12" s="5" t="n">
+        <x:v>3367000</x:v>
+      </x:c>
+      <x:c r="AG12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
-      <x:c r="AF12" s="5" t="n">
+      <x:c r="AH12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
-      <x:c r="AG12" s="5" t="n">
-        <x:v>3367000</x:v>
-      </x:c>
-      <x:c r="AH12" s="5" t="n">
-        <x:v>3367000</x:v>
-      </x:c>
       <x:c r="AI12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="AJ12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3454,7 +3454,7 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="AZ12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="BA12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3463,7 +3463,7 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BC12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="BD12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3475,16 +3475,16 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BG12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="BH12" s="5" t="n">
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="BI12" s="5" t="n">
-        <x:v>2886000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="BJ12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="BK12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3559,25 +3559,25 @@
         <x:v>2765750</x:v>
       </x:c>
       <x:c r="CI12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="CJ12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="CK12" s="5" t="n">
-        <x:v>2765750</x:v>
+        <x:v>3367000</x:v>
       </x:c>
       <x:c r="CL12" s="5" t="n">
         <x:v>3367000</x:v>
       </x:c>
       <x:c r="CM12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="CN12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="CO12" s="5" t="n">
-        <x:v>3367000</x:v>
+        <x:v>3607500</x:v>
       </x:c>
       <x:c r="CP12" s="5" t="n">
         <x:v>3607500</x:v>
@@ -3595,13 +3595,13 @@
         <x:v>3607500</x:v>
       </x:c>
       <x:c r="CU12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="CV12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="CW12" s="5" t="n">
-        <x:v>3607500</x:v>
+        <x:v>2765750</x:v>
       </x:c>
       <x:c r="CX12" s="5" t="n">
         <x:v>2765750</x:v>
@@ -3620,98 +3620,98 @@
       <x:c r="C14" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D14" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="3" t="n">
+      <x:c r="G14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q14" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="U14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="n">
+      <x:c r="V14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA14" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="U14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="W14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AA14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AC14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="AD14" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AE14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AF14" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="AF14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AG14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AH14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AI14" s="3" t="s">
         <x:v>3</x:v>
@@ -3719,38 +3719,38 @@
       <x:c r="AJ14" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AK14" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AL14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AK14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AL14" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AM14" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AN14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AO14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AN14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AO14" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AP14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AQ14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AR14" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AR14" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AS14" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AT14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AU14" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="AV14" s="3" t="n">
         <x:v>10</x:v>
@@ -3879,37 +3879,37 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="CL14" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CM14" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="CN14" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CO14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CP14" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CR14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CS14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CT14" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="CM14" s="3" t="n">
+      <x:c r="CU14" s="3" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="CN14" s="3" t="n">
+      <x:c r="CV14" s="3" t="n">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="CO14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CP14" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CQ14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CR14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CS14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CU14" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CV14" s="3" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="CW14" s="3" t="n">
         <x:v>10</x:v>
@@ -4249,13 +4249,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D16" s="5" t="n">
-        <x:v>4784000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="E16" s="5" t="n">
-        <x:v>4485000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="F16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="G16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4273,19 +4273,19 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="L16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>4485000</x:v>
       </x:c>
       <x:c r="M16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>4485000</x:v>
       </x:c>
       <x:c r="N16" s="5" t="n">
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="O16" s="5" t="n">
-        <x:v>4485000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="P16" s="5" t="n">
-        <x:v>4485000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="Q16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4309,7 +4309,7 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="X16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="Y16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4318,7 +4318,7 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="AA16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3588000</x:v>
       </x:c>
       <x:c r="AB16" s="5" t="n">
         <x:v>3588000</x:v>
@@ -4342,13 +4342,13 @@
         <x:v>3588000</x:v>
       </x:c>
       <x:c r="AI16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="AJ16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="AK16" s="5" t="n">
-        <x:v>3588000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="AL16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4411,7 +4411,7 @@
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="BF16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="BG16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4420,7 +4420,7 @@
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="BI16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="BJ16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4510,13 +4510,13 @@
         <x:v>3438500</x:v>
       </x:c>
       <x:c r="CM16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="CN16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="CO16" s="5" t="n">
-        <x:v>3438500</x:v>
+        <x:v>4186000</x:v>
       </x:c>
       <x:c r="CP16" s="5" t="n">
         <x:v>4186000</x:v>
@@ -4540,13 +4540,13 @@
         <x:v>4186000</x:v>
       </x:c>
       <x:c r="CW16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="CX16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="CY16" s="5" t="n">
-        <x:v>4186000</x:v>
+        <x:v>3438500</x:v>
       </x:c>
       <x:c r="CZ16" s="5" t="n">
         <x:v>3438500</x:v>
@@ -4562,41 +4562,41 @@
       <x:c r="D18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H18" s="3" t="n">
+      <x:c r="E18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="n">
+      <x:c r="F18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="n">
+      <x:c r="G18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="H18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="K18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="L18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M18" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="M18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P18" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q18" s="3" t="n">
         <x:v>0</x:v>
@@ -4605,244 +4605,244 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="T18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="U18" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X18" s="3" t="n">
+      <x:c r="W18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AB18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y18" s="3" t="n">
+      <x:c r="AE18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AF18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AG18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AK18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AM18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AN18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AO18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AP18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AQ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AR18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AS18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AT18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AU18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AV18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AX18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AY18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AZ18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BA18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BB18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BE18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BF18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BG18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BH18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BI18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BK18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BL18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BM18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BN18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BO18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BP18" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BU18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BV18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BX18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BY18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BZ18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CB18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CD18" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Z18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AD18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AE18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AF18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AG18" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AI18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AJ18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AK18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AN18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AO18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AP18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AQ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AR18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AS18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AT18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AU18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AV18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AW18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AX18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AY18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AZ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BA18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BB18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BC18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BD18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BE18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BG18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BH18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BI18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BJ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BK18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BL18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BN18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BO18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BP18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BQ18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BR18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BS18" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BT18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BX18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BY18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BZ18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CA18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CB18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CC18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="CE18" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="CE18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CF18" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="CG18" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="CH18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CI18" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CJ18" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="CG18" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CH18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI18" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ18" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CK18" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="CL18" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="CL18" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CM18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CN18" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO18" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="CO18" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CP18" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CQ18" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CR18" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="CS18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CT18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CU18" s="3" t="n">
         <x:v>2</x:v>
@@ -4860,7 +4860,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CZ18" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:104">
@@ -5188,13 +5188,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="5" t="n">
-        <x:v>5772000</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="E20" s="5" t="n">
-        <x:v>5411250</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="F20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="G20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5212,19 +5212,19 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="L20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>5411250</x:v>
       </x:c>
       <x:c r="M20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>5411250</x:v>
       </x:c>
       <x:c r="N20" s="5" t="n">
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="O20" s="5" t="n">
-        <x:v>5411250</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="P20" s="5" t="n">
-        <x:v>5411250</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="Q20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5248,7 +5248,7 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="X20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="Y20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5257,7 +5257,7 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="AA20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4329000</x:v>
       </x:c>
       <x:c r="AB20" s="5" t="n">
         <x:v>4329000</x:v>
@@ -5281,13 +5281,13 @@
         <x:v>4329000</x:v>
       </x:c>
       <x:c r="AI20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="AJ20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="AK20" s="5" t="n">
-        <x:v>4329000</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="AL20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5350,7 +5350,7 @@
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="BF20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="BG20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5359,7 +5359,7 @@
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="BI20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="BJ20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5449,13 +5449,13 @@
         <x:v>4148625</x:v>
       </x:c>
       <x:c r="CM20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="CN20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="CO20" s="5" t="n">
-        <x:v>4148625</x:v>
+        <x:v>5050500</x:v>
       </x:c>
       <x:c r="CP20" s="5" t="n">
         <x:v>5050500</x:v>
@@ -5479,13 +5479,13 @@
         <x:v>5050500</x:v>
       </x:c>
       <x:c r="CW20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="CX20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="CY20" s="5" t="n">
-        <x:v>5050500</x:v>
+        <x:v>4148625</x:v>
       </x:c>
       <x:c r="CZ20" s="5" t="n">
         <x:v>4148625</x:v>
@@ -5498,110 +5498,110 @@
       <x:c r="C22" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E22" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R22" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P22" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q22" s="3" t="n">
+      <x:c r="T22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="S22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T22" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="U22" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="V22" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="W22" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="X22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y22" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z22" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA22" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AB22" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AC22" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC22" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD22" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AE22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AF22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AG22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AH22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AI22" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AK22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AL22" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AM22" s="3" t="n">
         <x:v>3</x:v>
@@ -5625,19 +5625,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AT22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AU22" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AV22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AW22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AX22" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AY22" s="3" t="n">
         <x:v>4</x:v>
@@ -5649,7 +5649,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="BB22" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BC22" s="3" t="n">
         <x:v>4</x:v>
@@ -5661,94 +5661,94 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="BF22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BG22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BH22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BI22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BK22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BL22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BM22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BN22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BO22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BP22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BG22" s="3" t="n">
+      <x:c r="BQ22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BR22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BT22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BU22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BV22" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BW22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BX22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BY22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BZ22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CA22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CB22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CC22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CD22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CE22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CF22" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CG22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BH22" s="3" t="n">
+      <x:c r="CH22" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BI22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BJ22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BK22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BL22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BN22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BO22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BP22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BQ22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BR22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BS22" s="3" t="n">
+      <x:c r="CI22" s="3" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="BT22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BU22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BV22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BW22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BX22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BY22" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BZ22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CA22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CB22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CC22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CD22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CE22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CF22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CG22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CH22" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CI22" s="3" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="CJ22" s="3" t="n">
         <x:v>4</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="CZ22" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:104">
@@ -6289,7 +6289,7 @@
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="BF24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="BG24" s="5" t="n">
         <x:v>5157750</x:v>
@@ -6298,7 +6298,7 @@
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="BI24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
       <x:c r="BJ24" s="5" t="n">
         <x:v>5157750</x:v>
@@ -6388,13 +6388,13 @@
         <x:v>5157750</x:v>
       </x:c>
       <x:c r="CM24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="CN24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="CO24" s="5" t="n">
-        <x:v>5157750</x:v>
+        <x:v>6279000</x:v>
       </x:c>
       <x:c r="CP24" s="5" t="n">
         <x:v>6279000</x:v>
@@ -6418,13 +6418,13 @@
         <x:v>6279000</x:v>
       </x:c>
       <x:c r="CW24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
       <x:c r="CX24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
       <x:c r="CY24" s="5" t="n">
-        <x:v>6279000</x:v>
+        <x:v>5157750</x:v>
       </x:c>
       <x:c r="CZ24" s="5" t="n">
         <x:v>5157750</x:v>
@@ -6444,55 +6444,55 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R26" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M26" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N26" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="P26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Q26" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="S26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="T26" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="U26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="V26" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W26" s="3" t="n">
         <x:v>0</x:v>
@@ -6500,20 +6500,20 @@
       <x:c r="X26" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="Y26" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Z26" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="Y26" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z26" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA26" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB26" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC26" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AC26" s="3" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD26" s="3" t="n">
         <x:v>5</x:v>
@@ -6522,16 +6522,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AH26" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AI26" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ26" s="3" t="n">
         <x:v>5</x:v>
@@ -6738,7 +6738,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="CZ26" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:104">
@@ -7228,7 +7228,7 @@
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="BF28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="BG28" s="5" t="n">
         <x:v>5494125</x:v>
@@ -7237,7 +7237,7 @@
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="BI28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
       <x:c r="BJ28" s="5" t="n">
         <x:v>5494125</x:v>
@@ -7327,13 +7327,13 @@
         <x:v>5494125</x:v>
       </x:c>
       <x:c r="CM28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="CN28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="CO28" s="5" t="n">
-        <x:v>5494125</x:v>
+        <x:v>6688500</x:v>
       </x:c>
       <x:c r="CP28" s="5" t="n">
         <x:v>6688500</x:v>
@@ -7357,13 +7357,13 @@
         <x:v>6688500</x:v>
       </x:c>
       <x:c r="CW28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
       <x:c r="CX28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
       <x:c r="CY28" s="5" t="n">
-        <x:v>6688500</x:v>
+        <x:v>5494125</x:v>
       </x:c>
       <x:c r="CZ28" s="5" t="n">
         <x:v>5494125</x:v>
@@ -7379,62 +7379,62 @@
       <x:c r="D30" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F30" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="E30" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G30" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I30" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I30" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J30" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M30" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="N30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="O30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P30" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="Q30" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="R30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="U30" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="V30" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="W30" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="V30" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W30" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X30" s="3" t="s">
         <x:v>3</x:v>
@@ -7445,20 +7445,20 @@
       <x:c r="Z30" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AA30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB30" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AC30" s="3" t="s">
+      <x:c r="AA30" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AB30" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AD30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AE30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AF30" s="3" t="n">
         <x:v>3</x:v>
@@ -7470,25 +7470,25 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AI30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AJ30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AK30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AL30" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AM30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AN30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AO30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AP30" s="3" t="n">
         <x:v>3</x:v>
@@ -7521,7 +7521,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AZ30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BA30" s="3" t="n">
         <x:v>3</x:v>
@@ -7530,7 +7530,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BC30" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BD30" s="3" t="n">
         <x:v>3</x:v>
@@ -7677,7 +7677,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CZ30" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:104">
@@ -8167,7 +8167,7 @@
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="BF32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="BG32" s="5" t="n">
         <x:v>6877000</x:v>
@@ -8176,7 +8176,7 @@
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="BI32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
       <x:c r="BJ32" s="5" t="n">
         <x:v>6877000</x:v>
@@ -8266,13 +8266,13 @@
         <x:v>6877000</x:v>
       </x:c>
       <x:c r="CM32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="CN32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="CO32" s="5" t="n">
-        <x:v>6877000</x:v>
+        <x:v>8372000</x:v>
       </x:c>
       <x:c r="CP32" s="5" t="n">
         <x:v>8372000</x:v>
@@ -8296,13 +8296,13 @@
         <x:v>8372000</x:v>
       </x:c>
       <x:c r="CW32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
       <x:c r="CX32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
       <x:c r="CY32" s="5" t="n">
-        <x:v>8372000</x:v>
+        <x:v>6877000</x:v>
       </x:c>
       <x:c r="CZ32" s="5" t="n">
         <x:v>6877000</x:v>
@@ -8315,29 +8315,29 @@
       <x:c r="C34" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D34" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D34" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G34" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I34" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="H34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I34" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J34" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K34" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L34" s="3" t="n">
         <x:v>3</x:v>
@@ -8346,247 +8346,247 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N34" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="O34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q34" s="3" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="T34" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U34" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V34" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="X34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Y34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="Z34" s="3" t="n">
+      <x:c r="X34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA34" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AB34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AC34" s="3" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AD34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AA34" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AB34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AC34" s="3" t="n">
+      <x:c r="AE34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AD34" s="3" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="AE34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="AF34" s="3" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG34" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AI34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AJ34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AL34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AM34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AN34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AO34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AJ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AK34" s="3" t="n">
+      <x:c r="AT34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AU34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AV34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AX34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AL34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AM34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AO34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AP34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AQ34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AR34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV34" s="3" t="n">
+      <x:c r="AY34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AZ34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AW34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AX34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AY34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AZ34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="BA34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BB34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BB34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="BC34" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="BD34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE34" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BF34" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BH34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BI34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BJ34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BD34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BE34" s="3" t="n">
+      <x:c r="BK34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BL34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BM34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BN34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BO34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BP34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BQ34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BF34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BG34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BH34" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BJ34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BK34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BL34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BM34" s="3" t="n">
+      <x:c r="BR34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BS34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BT34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BU34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BV34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BW34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BX34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BY34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="BZ34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CA34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CB34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CC34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CD34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CE34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CF34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CG34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CH34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CI34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CJ34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CK34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CL34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CM34" s="3" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="CN34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BN34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BO34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BP34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BQ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BR34" s="3" t="n">
+      <x:c r="CO34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="BS34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BT34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BU34" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="BV34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BW34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BX34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="BY34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="BZ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CA34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CB34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CC34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CD34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CE34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CF34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CG34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CH34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CI34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CJ34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CK34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CL34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CM34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CN34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="CO34" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="CP34" s="3" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="CQ34" s="3" t="n">
         <x:v>4</x:v>
@@ -8595,28 +8595,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="CS34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CT34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CU34" s="3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="CV34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="CT34" s="3" t="n">
+      <x:c r="CW34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="CU34" s="3" t="n">
+      <x:c r="CX34" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="CV34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CW34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="CX34" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="CY34" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="CZ34" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:104">
@@ -9106,7 +9106,7 @@
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="BF36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="BG36" s="5" t="n">
         <x:v>7736625</x:v>
@@ -9115,7 +9115,7 @@
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="BI36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
       <x:c r="BJ36" s="5" t="n">
         <x:v>7736625</x:v>
@@ -9205,13 +9205,13 @@
         <x:v>7736625</x:v>
       </x:c>
       <x:c r="CM36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="CN36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="CO36" s="5" t="n">
-        <x:v>7736625</x:v>
+        <x:v>9418500</x:v>
       </x:c>
       <x:c r="CP36" s="5" t="n">
         <x:v>9418500</x:v>
@@ -9235,13 +9235,13 @@
         <x:v>9418500</x:v>
       </x:c>
       <x:c r="CW36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
       <x:c r="CX36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
       <x:c r="CY36" s="5" t="n">
-        <x:v>9418500</x:v>
+        <x:v>7736625</x:v>
       </x:c>
       <x:c r="CZ36" s="5" t="n">
         <x:v>7736625</x:v>
@@ -9260,44 +9260,44 @@
       <x:c r="E38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G38" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="F38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I38" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="I38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J38" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L38" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="K38" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="O38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="P38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Q38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S38" s="3" t="n">
         <x:v>3</x:v>
@@ -9308,38 +9308,38 @@
       <x:c r="U38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="V38" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="V38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W38" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X38" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Y38" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Z38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA38" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB38" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AC38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AD38" s="3" t="n">
+      <x:c r="AC38" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AE38" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AF38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF38" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AG38" s="3" t="s">
         <x:v>3</x:v>
@@ -9353,29 +9353,29 @@
       <x:c r="AJ38" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AK38" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AM38" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AN38" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AK38" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AL38" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM38" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AN38" s="3" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AO38" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AP38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AQ38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AS38" s="3" t="n">
         <x:v>3</x:v>
@@ -9423,13 +9423,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BH38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BI38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BJ38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BK38" s="3" t="n">
         <x:v>2</x:v>
@@ -9444,13 +9444,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BO38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BP38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BQ38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="BR38" s="3" t="n">
         <x:v>3</x:v>
@@ -9471,22 +9471,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="BX38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BY38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BZ38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CA38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CB38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CC38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CD38" s="3" t="n">
         <x:v>3</x:v>
@@ -9510,31 +9510,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="CK38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CL38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CM38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CN38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CO38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CP38" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="CQ38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CR38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CS38" s="3" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="CT38" s="3" t="n">
         <x:v>2</x:v>
@@ -10045,7 +10045,7 @@
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="BF40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="BG40" s="5" t="n">
         <x:v>7475000</x:v>
@@ -10054,7 +10054,7 @@
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="BI40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
       <x:c r="BJ40" s="5" t="n">
         <x:v>7475000</x:v>
@@ -10144,13 +10144,13 @@
         <x:v>7475000</x:v>
       </x:c>
       <x:c r="CM40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="CN40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="CO40" s="5" t="n">
-        <x:v>7475000</x:v>
+        <x:v>9100000</x:v>
       </x:c>
       <x:c r="CP40" s="5" t="n">
         <x:v>9100000</x:v>
@@ -10174,13 +10174,13 @@
         <x:v>9100000</x:v>
       </x:c>
       <x:c r="CW40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
       <x:c r="CX40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
       <x:c r="CY40" s="5" t="n">
-        <x:v>9100000</x:v>
+        <x:v>7475000</x:v>
       </x:c>
       <x:c r="CZ40" s="5" t="n">
         <x:v>7475000</x:v>
@@ -10193,23 +10193,23 @@
       <x:c r="C42" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D42" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E42" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D42" s="3" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="3" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F42" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="3" t="n">
-        <x:v>0</x:v>
+      <x:c r="H42" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I42" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J42" s="3" t="n">
         <x:v>0</x:v>
@@ -10218,119 +10218,119 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L42" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O42" s="3" t="n">
+      <x:c r="S42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="P42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="R42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="S42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T42" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="T42" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Y42" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z42" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AE42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AP42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AT42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="V42" s="3" t="n">
+      <x:c r="AV42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AW42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W42" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="X42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Y42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Z42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AE42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AF42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AG42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AH42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AI42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AJ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AP42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AR42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AV42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AW42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="AX42" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -10338,157 +10338,157 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AZ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BA42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BD42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BE42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BG42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BH42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BM42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BP42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BT42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BU42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BV42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BW42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BX42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BY42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BZ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CA42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CB42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CC42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CD42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="BA42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BB42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BE42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BF42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BG42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BH42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BI42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BJ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BP42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BR42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BV42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BW42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BX42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BY42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="BZ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CA42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CB42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CC42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CD42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="CE42" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="CF42" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="CG42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CH42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CI42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CJ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CK42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CL42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CM42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CH42" s="3" t="n">
+      <x:c r="CN42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CO42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CP42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CQ42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CR42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CS42" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="CT42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CI42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CJ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CK42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CL42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CM42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CN42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CO42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CP42" s="3" t="n">
+      <x:c r="CU42" s="3" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="CQ42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CR42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CS42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CT42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="CU42" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="CV42" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="CW42" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CX42" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="CY42" s="3" t="n">
         <x:v>1</x:v>
@@ -11144,11 +11144,11 @@
       <x:c r="G46" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I46" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="H46" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I46" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J46" s="3" t="n">
         <x:v>1</x:v>
@@ -11156,23 +11156,23 @@
       <x:c r="K46" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L46" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="L46" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="P46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="Q46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R46" s="3" t="n">
         <x:v>2</x:v>
@@ -11192,14 +11192,14 @@
       <x:c r="W46" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X46" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Y46" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Z46" s="3" t="n">
-        <x:v>2</x:v>
+      <x:c r="X46" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Y46" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Z46" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA46" s="3" t="n">
         <x:v>2</x:v>
@@ -11235,25 +11235,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AM46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AN46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AO46" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AP46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AQ46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AS46" s="3" t="n">
         <x:v>2</x:v>
@@ -11277,25 +11277,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AZ46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BA46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BB46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BC46" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="BD46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BE46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BF46" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BG46" s="3" t="n">
         <x:v>2</x:v>
@@ -11319,16 +11319,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="BN46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BO46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BP46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BQ46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BR46" s="3" t="n">
         <x:v>2</x:v>
@@ -11433,7 +11433,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="CZ46" s="3" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:104">
@@ -11923,7 +11923,7 @@
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="BF48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="BG48" s="5" t="n">
         <x:v>9941750</x:v>
@@ -11932,7 +11932,7 @@
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="BI48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
       <x:c r="BJ48" s="5" t="n">
         <x:v>9941750</x:v>
@@ -12022,13 +12022,13 @@
         <x:v>9941750</x:v>
       </x:c>
       <x:c r="CM48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="CN48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="CO48" s="5" t="n">
-        <x:v>9941750</x:v>
+        <x:v>12103000</x:v>
       </x:c>
       <x:c r="CP48" s="5" t="n">
         <x:v>12103000</x:v>
@@ -12052,13 +12052,13 @@
         <x:v>12103000</x:v>
       </x:c>
       <x:c r="CW48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
       <x:c r="CX48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
       <x:c r="CY48" s="5" t="n">
-        <x:v>12103000</x:v>
+        <x:v>9941750</x:v>
       </x:c>
       <x:c r="CZ48" s="5" t="n">
         <x:v>9941750</x:v>
@@ -12071,11 +12071,11 @@
       <x:c r="C50" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D50" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E50" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="D50" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F50" s="3" t="n">
         <x:v>1</x:v>
@@ -12083,11 +12083,11 @@
       <x:c r="G50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H50" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="H50" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J50" s="3" t="n">
         <x:v>1</x:v>
@@ -12111,19 +12111,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q50" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="R50" s="3" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="S50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T50" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="U50" s="3" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V50" s="3" t="n">
         <x:v>1</x:v>
@@ -12137,17 +12137,17 @@
       <x:c r="Y50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Z50" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AA50" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AB50" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AC50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="Z50" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AA50" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AB50" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD50" s="3" t="s">
         <x:v>3</x:v>
@@ -12164,14 +12164,14 @@
       <x:c r="AH50" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AI50" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AJ50" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AK50" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AI50" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ50" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AK50" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AL50" s="3" t="n">
         <x:v>1</x:v>
@@ -12203,8 +12203,8 @@
       <x:c r="AU50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AV50" s="3" t="n">
-        <x:v>1</x:v>
+      <x:c r="AV50" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW50" s="3" t="n">
         <x:v>1</x:v>
@@ -12212,8 +12212,8 @@
       <x:c r="AX50" s="3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AY50" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="AY50" s="3" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AZ50" s="3" t="n">
         <x:v>1</x:v>
